--- a/consent_forms/039_court_objection_and_consent_form--consent_forms.xlsx
+++ b/consent_forms/039_court_objection_and_consent_form--consent_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_page_1</t>
+          <t>parties_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>party_contact_info_1</t>
+          <t>party_1_contact_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>party_name_1</t>
+          <t>party_1_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Party 1 Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>party_name_1_hints</t>
+          <t>party_1_email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Party 1 Name</t>
+          <t>Party 1 Email</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>party_email_1</t>
+          <t>party_1_phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Party 1 Phone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>party_phone_1</t>
+          <t>party_2_contact_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Party 2 Contact Information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>party_contact_info_2</t>
+          <t>party_2_name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Party 2 Contact Information</t>
+          <t>Party 2 Name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>party_name_2</t>
+          <t>party_2_email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Party 2 Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>party_email_2</t>
+          <t>party_2_phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Party 2 Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>party_phone_2</t>
+          <t>party_3_contact_info</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Party 3 Contact Information</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>party_name_3</t>
+          <t>party_3_name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Party 3 Name</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>party_contact_info_3</t>
+          <t>party_3_email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Party 3 Contact Information</t>
+          <t>Party 3 Email</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>party_name_3_hints</t>
+          <t>party_3_phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Party 3 Name</t>
+          <t>Party 3 Phone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>party_email_3</t>
+          <t>party_4_contact_info</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Party 4 Contact Information</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>party_phone_3</t>
+          <t>party_4_name</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Party 4 Name</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>party_contact_info_4</t>
+          <t>party_4_email</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Party 4 Contact Information</t>
+          <t>Party 4 Email</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>party_name_4</t>
+          <t>party_4_phone</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Party 4 Phone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>party_email_4</t>
+          <t>case_reference</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Case Reference</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>party_phone_4</t>
+          <t>written_statement</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Written Statement</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,131 +947,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>case_reference</t>
+          <t>acknowledgment</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Case Reference</t>
+          <t>Acknowledgment</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>written_statement_1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Written Statement 1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>written_statement_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Written Statement 2</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>written_statement_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Written Statement 3</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>written_statement_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Written Statement 4</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>acknowledgment</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Acknowledgment</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
